--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.36825354073949</v>
+        <v>8.347341200370167</v>
       </c>
       <c r="D2" t="n">
-        <v>50.55061184633175</v>
+        <v>8.214474425028911</v>
       </c>
       <c r="E2" t="n">
-        <v>14.29728281583168</v>
+        <v>2.323308457572649</v>
       </c>
       <c r="F2" t="n">
-        <v>16.07394953321732</v>
+        <v>2.612016799147814</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.07971445268823</v>
+        <v>6.512953598561838</v>
       </c>
       <c r="D3" t="n">
-        <v>9.178409986296272</v>
+        <v>1.491491622773144</v>
       </c>
       <c r="E3" t="n">
-        <v>14.29728281583168</v>
+        <v>2.323308457572649</v>
       </c>
       <c r="F3" t="n">
-        <v>16.07394953321732</v>
+        <v>2.612016799147814</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.64472316622181</v>
+        <v>3.842267514511045</v>
       </c>
       <c r="D4" t="n">
-        <v>23.84316736207419</v>
+        <v>3.874514696337056</v>
       </c>
       <c r="E4" t="n">
-        <v>14.29728281583168</v>
+        <v>2.323308457572649</v>
       </c>
       <c r="F4" t="n">
-        <v>16.07394953321732</v>
+        <v>2.612016799147814</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>9.195308364841875</v>
+        <v>1.494237609286805</v>
       </c>
       <c r="D5" t="n">
-        <v>9.210522293573478</v>
+        <v>1.49670987270569</v>
       </c>
       <c r="E5" t="n">
-        <v>14.29728281583168</v>
+        <v>2.323308457572649</v>
       </c>
       <c r="F5" t="n">
-        <v>16.07394953321732</v>
+        <v>2.612016799147814</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.65466532247427</v>
+        <v>5.793883114902069</v>
       </c>
       <c r="D6" t="n">
-        <v>35.69950785557204</v>
+        <v>5.801170026530458</v>
       </c>
       <c r="E6" t="n">
-        <v>14.29728281583168</v>
+        <v>2.323308457572649</v>
       </c>
       <c r="F6" t="n">
-        <v>16.07394953321732</v>
+        <v>2.612016799147814</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.80375339503091</v>
+        <v>3.705609926692524</v>
       </c>
       <c r="D7" t="n">
-        <v>22.60915142164036</v>
+        <v>3.673987106016558</v>
       </c>
       <c r="E7" t="n">
-        <v>14.29728281583168</v>
+        <v>2.323308457572649</v>
       </c>
       <c r="F7" t="n">
-        <v>16.07394953321732</v>
+        <v>2.612016799147814</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>49.68740325119445</v>
+        <v>8.074203028319097</v>
       </c>
       <c r="D8" t="n">
-        <v>50.16063490270928</v>
+        <v>8.151103171690258</v>
       </c>
       <c r="E8" t="n">
-        <v>14.29728281583168</v>
+        <v>2.323308457572649</v>
       </c>
       <c r="F8" t="n">
-        <v>16.07394953321732</v>
+        <v>2.612016799147814</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
